--- a/Data/Input/Dicc_INV.xlsx
+++ b/Data/Input/Dicc_INV.xlsx
@@ -496,94 +496,94 @@
     <t>14107</t>
   </si>
   <si>
-    <t>MM17517413</t>
-  </si>
-  <si>
-    <t>MM17501657</t>
-  </si>
-  <si>
-    <t>MM54859039</t>
-  </si>
-  <si>
-    <t>MM17521757</t>
-  </si>
-  <si>
-    <t>MM17568191</t>
-  </si>
-  <si>
-    <t>MM18552866</t>
-  </si>
-  <si>
-    <t>MM17624697</t>
-  </si>
-  <si>
-    <t>MM17500709</t>
-  </si>
-  <si>
-    <t>MM17534831</t>
-  </si>
-  <si>
-    <t>MM17621841</t>
-  </si>
-  <si>
-    <t>MM17520123</t>
-  </si>
-  <si>
-    <t>MM17841391</t>
-  </si>
-  <si>
-    <t>MM18543903</t>
-  </si>
-  <si>
-    <t>MM98173543</t>
-  </si>
-  <si>
-    <t>MM17766695</t>
-  </si>
-  <si>
-    <t>MM17500963</t>
-  </si>
-  <si>
-    <t>MM17526449</t>
-  </si>
-  <si>
-    <t>MM17521713</t>
-  </si>
-  <si>
-    <t>MM17585171</t>
-  </si>
-  <si>
-    <t>MM18562458</t>
-  </si>
-  <si>
-    <t>MM17590061</t>
-  </si>
-  <si>
-    <t>MM17573733</t>
-  </si>
-  <si>
-    <t>MM74119073</t>
-  </si>
-  <si>
-    <t>MM101950490</t>
-  </si>
-  <si>
-    <t>MM17557253</t>
-  </si>
-  <si>
-    <t>MM100003356</t>
-  </si>
-  <si>
-    <t>MM100032036</t>
-  </si>
-  <si>
-    <t>MM18543154</t>
-  </si>
-  <si>
-    <t>MM18543152</t>
-  </si>
-  <si>
-    <t>MM17514909</t>
+    <t>MM99997413</t>
+  </si>
+  <si>
+    <t>MM99991657</t>
+  </si>
+  <si>
+    <t>MM99999039</t>
+  </si>
+  <si>
+    <t>MM99991757</t>
+  </si>
+  <si>
+    <t>MM99998191</t>
+  </si>
+  <si>
+    <t>MM99992866</t>
+  </si>
+  <si>
+    <t>MM99994697</t>
+  </si>
+  <si>
+    <t>MM99990709</t>
+  </si>
+  <si>
+    <t>MM99994831</t>
+  </si>
+  <si>
+    <t>MM99991841</t>
+  </si>
+  <si>
+    <t>MM99990123</t>
+  </si>
+  <si>
+    <t>MM99991391</t>
+  </si>
+  <si>
+    <t>MM99993903</t>
+  </si>
+  <si>
+    <t>MM99993543</t>
+  </si>
+  <si>
+    <t>MM99996695</t>
+  </si>
+  <si>
+    <t>MM99990963</t>
+  </si>
+  <si>
+    <t>MM99996449</t>
+  </si>
+  <si>
+    <t>MM99991713</t>
+  </si>
+  <si>
+    <t>MM99995171</t>
+  </si>
+  <si>
+    <t>MM99992458</t>
+  </si>
+  <si>
+    <t>MM99990061</t>
+  </si>
+  <si>
+    <t>MM99993733</t>
+  </si>
+  <si>
+    <t>MM99999073</t>
+  </si>
+  <si>
+    <t>MM999950490</t>
+  </si>
+  <si>
+    <t>MM99997253</t>
+  </si>
+  <si>
+    <t>MM999903356</t>
+  </si>
+  <si>
+    <t>MM999932036</t>
+  </si>
+  <si>
+    <t>MM99993154</t>
+  </si>
+  <si>
+    <t>MM99993152</t>
+  </si>
+  <si>
+    <t>MM99994909</t>
   </si>
   <si>
     <t>|1415-5|1425-3|</t>
